--- a/Side Bar Files/GWD Data/TW Casing Pipes.xlsx
+++ b/Side Bar Files/GWD Data/TW Casing Pipes.xlsx
@@ -317,7 +317,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_8" displayName="Table_8" ref="A1:D7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_10" displayName="Table_10" ref="A1:D7">
   <tableColumns count="4">
     <tableColumn id="1" name="Spec Code"/>
     <tableColumn id="2" name="Specification"/>
@@ -329,7 +329,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table_9" displayName="Table_9" ref="A9:D11" headerRowCount="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table_11" displayName="Table_11" ref="A9:D11" headerRowCount="0">
   <tableColumns count="4">
     <tableColumn id="1" name="Column1"/>
     <tableColumn id="2" name="Column2"/>
@@ -341,7 +341,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table_10" displayName="Table_10" ref="A12:D13" headerRowCount="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table_12" displayName="Table_12" ref="A12:D13" headerRowCount="0">
   <tableColumns count="4">
     <tableColumn id="1" name="Column1"/>
     <tableColumn id="2" name="Column2"/>
@@ -648,7 +648,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89DDE1DC-DEC7-4C18-BD2F-DCA4E07EB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED44AEC-B001-4826-AD74-43B832D7B9A7}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/TW Casing Pipes.xlsx
+++ b/Side Bar Files/GWD Data/TW Casing Pipes.xlsx
@@ -154,25 +154,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -190,11 +176,11 @@
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -317,7 +303,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_10" displayName="Table_10" ref="A1:D7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_9" displayName="Table_9" ref="A1:D7">
   <tableColumns count="4">
     <tableColumn id="1" name="Spec Code"/>
     <tableColumn id="2" name="Specification"/>
@@ -329,7 +315,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table_11" displayName="Table_11" ref="A9:D11" headerRowCount="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table_10" displayName="Table_10" ref="A9:D11" headerRowCount="0">
   <tableColumns count="4">
     <tableColumn id="1" name="Column1"/>
     <tableColumn id="2" name="Column2"/>
@@ -341,7 +327,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table_12" displayName="Table_12" ref="A12:D13" headerRowCount="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table_11" displayName="Table_11" ref="A12:D13" headerRowCount="0">
   <tableColumns count="4">
     <tableColumn id="1" name="Column1"/>
     <tableColumn id="2" name="Column2"/>
@@ -648,7 +634,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ED44AEC-B001-4826-AD74-43B832D7B9A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D429CE8-5ABB-43B9-A153-4B57F12CBAA6}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/TW Casing Pipes.xlsx
+++ b/Side Bar Files/GWD Data/TW Casing Pipes.xlsx
@@ -634,7 +634,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D429CE8-5ABB-43B9-A153-4B57F12CBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CF91C58-BA91-41ED-9005-0E8AAF73BAA6}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/TW Casing Pipes.xlsx
+++ b/Side Bar Files/GWD Data/TW Casing Pipes.xlsx
@@ -634,7 +634,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CF91C58-BA91-41ED-9005-0E8AAF73BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C108873B-9FA7-4EC7-B501-2D36BDD4BAA6}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
